--- a/data/trans_dic/P37-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P37-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha vacunado de la gripe en la última campaña</t>
+          <t>Población que se ha vacunado de la gripe en la última campaña (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,78; 19,29</t>
+          <t>10,73; 19,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,82; 22,02</t>
+          <t>12,68; 21,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,19; 19,48</t>
+          <t>10,6; 19,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,59; 35,34</t>
+          <t>23,05; 34,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,4; 16,53</t>
+          <t>8,15; 16,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,25; 21,83</t>
+          <t>12,39; 21,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,75; 21,02</t>
+          <t>12,11; 21,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,64; 41,16</t>
+          <t>31,94; 41,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,75; 16,83</t>
+          <t>10,47; 16,33</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13,56; 19,96</t>
+          <t>13,38; 20,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,45; 18,45</t>
+          <t>12,27; 18,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,48; 35,94</t>
+          <t>28,99; 36,03</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,56; 13,35</t>
+          <t>7,86; 13,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,25; 21,79</t>
+          <t>14,54; 21,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,97; 19,76</t>
+          <t>12,9; 19,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,92; 31,79</t>
+          <t>22,44; 31,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,95; 15,77</t>
+          <t>9,69; 15,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,95; 20,77</t>
+          <t>14,22; 20,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,23; 16,91</t>
+          <t>10,59; 16,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,76; 34,79</t>
+          <t>27,67; 34,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,4; 13,41</t>
+          <t>9,46; 13,55</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,16; 20,21</t>
+          <t>14,94; 19,95</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12,58; 17,14</t>
+          <t>12,15; 17,01</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,19; 32,03</t>
+          <t>26,26; 32,24</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,54; 19,15</t>
+          <t>11,49; 19,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,41; 26,01</t>
+          <t>16,48; 25,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,01; 23,12</t>
+          <t>14,91; 23,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,82; 31,98</t>
+          <t>22,74; 31,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,75; 23,03</t>
+          <t>14,77; 23,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,16; 23,53</t>
+          <t>14,84; 23,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,17; 26,5</t>
+          <t>17,16; 26,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27,42; 35,22</t>
+          <t>26,96; 35,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,48; 20,43</t>
+          <t>14,26; 19,95</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,76; 22,78</t>
+          <t>16,82; 23,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,31; 23,64</t>
+          <t>17,47; 23,81</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,72; 32,43</t>
+          <t>26,4; 32,64</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,87; 15,91</t>
+          <t>9,25; 15,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,9; 22,41</t>
+          <t>13,77; 22,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,75; 23,81</t>
+          <t>15,52; 23,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,24; 38,31</t>
+          <t>26,5; 38,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,97; 20,12</t>
+          <t>13,25; 20,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,39; 28,44</t>
+          <t>19,7; 28,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,85; 25,62</t>
+          <t>17,39; 25,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,39; 36,25</t>
+          <t>16,99; 36,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,85; 16,91</t>
+          <t>12,13; 17,02</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,88; 23,96</t>
+          <t>17,8; 24,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,05; 23,48</t>
+          <t>17,11; 23,57</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,96; 35,59</t>
+          <t>21,72; 35,35</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,94; 21,05</t>
+          <t>10,81; 20,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,83; 23,11</t>
+          <t>11,72; 22,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,6; 18,13</t>
+          <t>9,22; 18,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,48; 37,01</t>
+          <t>25,91; 37,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,54; 26,93</t>
+          <t>14,91; 26,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,14; 25,21</t>
+          <t>14,08; 25,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,34; 19,35</t>
+          <t>9,57; 19,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,63; 43,63</t>
+          <t>34,3; 43,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,1; 21,58</t>
+          <t>14,17; 21,83</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,15; 21,78</t>
+          <t>14,59; 22,3</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,62; 17,21</t>
+          <t>10,22; 17,13</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,84; 38,85</t>
+          <t>32,1; 38,87</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,55; 17,57</t>
+          <t>9,36; 17,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,27; 26,11</t>
+          <t>16,54; 27,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,69; 24,22</t>
+          <t>14,59; 24,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22,74; 30,72</t>
+          <t>22,16; 30,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,58; 22,8</t>
+          <t>13,12; 22,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,42; 28,57</t>
+          <t>18,31; 28,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,42; 29,09</t>
+          <t>18,47; 28,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>32,71; 41,63</t>
+          <t>32,72; 41,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,22; 18,34</t>
+          <t>12,57; 18,71</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18,54; 26,04</t>
+          <t>18,62; 25,49</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18,16; 25,25</t>
+          <t>17,76; 25,26</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>28,59; 34,94</t>
+          <t>28,19; 34,85</t>
         </is>
       </c>
     </row>
@@ -1557,52 +1557,52 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,19; 18,11</t>
+          <t>12,54; 18,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,2; 20,34</t>
+          <t>13,98; 20,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,59; 19,73</t>
+          <t>13,75; 19,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27,56; 35,42</t>
+          <t>27,66; 35,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,46; 20,21</t>
+          <t>14,5; 20,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,8; 19,97</t>
+          <t>14,26; 19,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,34; 22,66</t>
+          <t>16,4; 22,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>35,08; 73,22</t>
+          <t>35,03; 76,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,9; 18,19</t>
+          <t>14,2; 18,29</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14,87; 19,24</t>
+          <t>15,07; 19,37</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33,01; 64,73</t>
+          <t>32,86; 62,83</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,79; 18,1</t>
+          <t>12,69; 18,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,28; 18,88</t>
+          <t>13,36; 18,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,94; 14,63</t>
+          <t>9,89; 14,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,55; 39,39</t>
+          <t>12,92; 39,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,38; 17,71</t>
+          <t>12,34; 17,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,45; 18,8</t>
+          <t>13,59; 18,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,38; 16,26</t>
+          <t>11,54; 16,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>39,0; 45,16</t>
+          <t>39,03; 45,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,36; 16,81</t>
+          <t>13,36; 17,03</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14,15; 18,05</t>
+          <t>14,23; 18,13</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11,23; 14,82</t>
+          <t>11,37; 14,79</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,56; 41,0</t>
+          <t>21,35; 41,15</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12,68; 14,97</t>
+          <t>12,76; 14,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,36; 19,13</t>
+          <t>16,42; 19,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14,53; 17,12</t>
+          <t>14,64; 17,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22,33; 31,85</t>
+          <t>22,0; 31,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,55; 17,08</t>
+          <t>14,63; 17,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,95; 19,61</t>
+          <t>16,97; 19,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,93; 18,62</t>
+          <t>16,03; 18,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>34,91; 50,92</t>
+          <t>34,77; 49,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14,07; 15,81</t>
+          <t>14,03; 15,72</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17,03; 18,89</t>
+          <t>16,91; 18,89</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15,56; 17,43</t>
+          <t>15,65; 17,44</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>30,79; 40,34</t>
+          <t>31,01; 40,25</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha vacunado de la gripe en la última campaña</t>
+          <t>Población que se ha vacunado de la gripe en la última campaña (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>29324; 52490</t>
+          <t>29205; 52450</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>37792; 64894</t>
+          <t>37373; 63472</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32880; 57212</t>
+          <t>31149; 56833</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>73477; 110054</t>
+          <t>71781; 106535</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21921; 43107</t>
+          <t>21253; 42686</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35180; 62694</t>
+          <t>35588; 62556</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33926; 60679</t>
+          <t>34976; 62467</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>91636; 119209</t>
+          <t>92515; 118940</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>57290; 89685</t>
+          <t>55801; 87018</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>78913; 116162</t>
+          <t>77853; 118129</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>72529; 107477</t>
+          <t>71444; 110423</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>171168; 216009</t>
+          <t>174264; 216546</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37270; 65820</t>
+          <t>38743; 66347</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>72048; 110164</t>
+          <t>73517; 110594</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>65203; 99318</t>
+          <t>64819; 97940</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>118819; 164795</t>
+          <t>116303; 163911</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>50037; 79313</t>
+          <t>48729; 76636</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>73039; 108783</t>
+          <t>74475; 109852</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>53537; 88443</t>
+          <t>55402; 86550</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>142939; 179134</t>
+          <t>142478; 179434</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93652; 133610</t>
+          <t>94227; 134998</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>156001; 207975</t>
+          <t>153784; 205315</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>129046; 175752</t>
+          <t>124574; 174424</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>270634; 331013</t>
+          <t>271377; 333163</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>36792; 61069</t>
+          <t>36645; 62692</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>52846; 83779</t>
+          <t>53087; 82582</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47812; 73638</t>
+          <t>47485; 73869</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>72137; 101065</t>
+          <t>71874; 100563</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>49469; 77253</t>
+          <t>49544; 78366</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>51541; 79984</t>
+          <t>50458; 79161</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57731; 89132</t>
+          <t>57702; 89600</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>95739; 122974</t>
+          <t>94123; 122824</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>94731; 133681</t>
+          <t>93328; 130501</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>110943; 150840</t>
+          <t>111325; 152660</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>113348; 154845</t>
+          <t>114399; 155894</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>177725; 215698</t>
+          <t>175578; 217095</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31801; 57077</t>
+          <t>33169; 56365</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51979; 83817</t>
+          <t>51488; 83142</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>58267; 88071</t>
+          <t>57422; 87550</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>82022; 119727</t>
+          <t>82835; 119202</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>48188; 74720</t>
+          <t>49224; 76025</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>75405; 110634</t>
+          <t>76627; 110358</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>65241; 99211</t>
+          <t>67365; 99910</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>82708; 172427</t>
+          <t>80836; 173707</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>86500; 123431</t>
+          <t>88571; 124267</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>136417; 182783</t>
+          <t>135796; 184772</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>129081; 177797</t>
+          <t>129577; 178476</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>180979; 280552</t>
+          <t>171174; 278664</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>22236; 42804</t>
+          <t>21986; 42512</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25023; 48893</t>
+          <t>24800; 48457</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20270; 38299</t>
+          <t>19478; 38664</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45540; 66150</t>
+          <t>46315; 66591</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>30068; 55681</t>
+          <t>30826; 53814</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31043; 55349</t>
+          <t>30909; 55455</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20425; 42299</t>
+          <t>20914; 42598</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>72131; 90863</t>
+          <t>71444; 90516</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>57803; 88496</t>
+          <t>58114; 89512</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>61017; 93935</t>
+          <t>62895; 96150</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45647; 73967</t>
+          <t>43947; 73611</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>123208; 150342</t>
+          <t>124247; 150431</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>25852; 47582</t>
+          <t>25340; 47373</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>44587; 71541</t>
+          <t>45325; 73968</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>38641; 63721</t>
+          <t>38399; 63893</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>61320; 82845</t>
+          <t>59758; 83287</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>37764; 63404</t>
+          <t>36482; 62721</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>51579; 79998</t>
+          <t>51276; 78694</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50298; 79450</t>
+          <t>50435; 78469</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>84093; 107022</t>
+          <t>84117; 106333</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>67056; 100662</t>
+          <t>68994; 102727</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>102723; 144269</t>
+          <t>103148; 141204</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>97382; 135373</t>
+          <t>95226; 135454</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>150565; 184004</t>
+          <t>148471; 183570</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>74896; 111247</t>
+          <t>77020; 112725</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>94091; 134809</t>
+          <t>92674; 135088</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>89212; 129540</t>
+          <t>90298; 129954</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>172026; 221126</t>
+          <t>172680; 221961</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>92305; 128981</t>
+          <t>92520; 130636</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>95737; 138535</t>
+          <t>98909; 138082</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>112992; 156634</t>
+          <t>113346; 157134</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>297942; 621831</t>
+          <t>297467; 646574</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>174095; 227754</t>
+          <t>177884; 229114</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>201726; 260984</t>
+          <t>204398; 262817</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>214960; 274645</t>
+          <t>214920; 274718</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>486364; 953869</t>
+          <t>484226; 925864</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>95133; 134625</t>
+          <t>94366; 133940</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>103192; 146721</t>
+          <t>103779; 146643</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>77406; 113889</t>
+          <t>76996; 112884</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>107268; 365814</t>
+          <t>119976; 367764</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>97026; 138743</t>
+          <t>96679; 138294</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>110767; 154901</t>
+          <t>111937; 155344</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>94039; 134300</t>
+          <t>95324; 138346</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>279028; 323051</t>
+          <t>279244; 326040</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>204022; 256731</t>
+          <t>204039; 260040</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>226509; 288915</t>
+          <t>227879; 290242</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>180186; 237825</t>
+          <t>182422; 237269</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>354399; 674165</t>
+          <t>350951; 676617</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>415220; 490166</t>
+          <t>417913; 490096</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>559635; 654722</t>
+          <t>561934; 651223</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>493254; 581097</t>
+          <t>496907; 576882</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>772581; 1102113</t>
+          <t>761251; 1094074</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>491392; 576847</t>
+          <t>494083; 574991</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>602855; 697599</t>
+          <t>603682; 697331</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>564712; 659929</t>
+          <t>568059; 664023</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1277459; 1863471</t>
+          <t>1272239; 1826627</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>936157; 1051755</t>
+          <t>933527; 1045896</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1188426; 1318334</t>
+          <t>1180465; 1318056</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1079768; 1209766</t>
+          <t>1085633; 1210414</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2191821; 2871650</t>
+          <t>2207379; 2865676</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P37-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P37-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>30,85%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,73; 19,28</t>
+          <t>10,67; 18,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,68; 21,54</t>
+          <t>12,53; 21,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,6; 19,35</t>
+          <t>10,97; 19,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,05; 34,21</t>
+          <t>23,73; 33,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,15; 16,37</t>
+          <t>8,25; 16,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,39; 21,78</t>
+          <t>12,16; 21,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,11; 21,64</t>
+          <t>12,1; 21,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,94; 41,07</t>
+          <t>29,41; 37,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,47; 16,33</t>
+          <t>10,59; 16,68</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13,38; 20,3</t>
+          <t>13,35; 19,97</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,27; 18,96</t>
+          <t>12,6; 18,76</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,99; 36,03</t>
+          <t>27,79; 34,18</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,86; 13,46</t>
+          <t>7,79; 13,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,54; 21,88</t>
+          <t>14,5; 21,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,9; 19,49</t>
+          <t>12,64; 19,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,44; 31,62</t>
+          <t>23,13; 31,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,69; 15,24</t>
+          <t>9,85; 15,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,22; 20,97</t>
+          <t>14,18; 21,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,59; 16,55</t>
+          <t>10,47; 16,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,67; 34,84</t>
+          <t>26,99; 34,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,46; 13,55</t>
+          <t>9,51; 13,54</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,94; 19,95</t>
+          <t>14,92; 20,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12,15; 17,01</t>
+          <t>12,59; 17,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,26; 32,24</t>
+          <t>26,5; 32,05</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,25%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,49; 19,66</t>
+          <t>11,26; 19,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,48; 25,64</t>
+          <t>16,84; 26,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,91; 23,19</t>
+          <t>14,84; 23,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,74; 31,82</t>
+          <t>23,28; 31,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,77; 23,36</t>
+          <t>14,56; 23,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,84; 23,29</t>
+          <t>14,37; 23,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,16; 26,64</t>
+          <t>17,47; 26,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26,96; 35,18</t>
+          <t>27,13; 35,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,26; 19,95</t>
+          <t>14,23; 20,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,82; 23,06</t>
+          <t>16,65; 22,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,47; 23,81</t>
+          <t>16,96; 23,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,4; 32,64</t>
+          <t>26,05; 31,94</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>32,32%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,25; 15,72</t>
+          <t>9,0; 15,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,77; 22,23</t>
+          <t>13,9; 22,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,52; 23,66</t>
+          <t>15,58; 23,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,5; 38,14</t>
+          <t>23,73; 34,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,25; 20,47</t>
+          <t>13,12; 20,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,7; 28,37</t>
+          <t>20,08; 28,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,39; 25,8</t>
+          <t>17,49; 26,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,99; 36,51</t>
+          <t>31,14; 39,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,13; 17,02</t>
+          <t>11,97; 16,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,8; 24,22</t>
+          <t>17,87; 23,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,11; 23,57</t>
+          <t>17,32; 23,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,72; 35,35</t>
+          <t>29,12; 35,34</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>33,62%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,81; 20,91</t>
+          <t>11,34; 21,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,72; 22,9</t>
+          <t>12,17; 22,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,22; 18,3</t>
+          <t>9,04; 18,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,91; 37,26</t>
+          <t>23,94; 34,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,91; 26,03</t>
+          <t>14,79; 25,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,08; 25,25</t>
+          <t>14,73; 25,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,57; 19,49</t>
+          <t>9,75; 19,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,3; 43,46</t>
+          <t>33,08; 42,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,17; 21,83</t>
+          <t>14,43; 21,85</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,59; 22,3</t>
+          <t>14,84; 22,03</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,22; 17,13</t>
+          <t>10,42; 16,88</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,1; 38,87</t>
+          <t>30,18; 36,88</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,63%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,36; 17,49</t>
+          <t>9,49; 17,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,54; 27,0</t>
+          <t>16,97; 26,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,59; 24,28</t>
+          <t>15,09; 24,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22,16; 30,89</t>
+          <t>22,25; 30,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,12; 22,55</t>
+          <t>13,59; 22,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,31; 28,1</t>
+          <t>18,3; 29,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,47; 28,73</t>
+          <t>18,79; 28,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>32,72; 41,37</t>
+          <t>32,13; 41,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,57; 18,71</t>
+          <t>12,45; 18,78</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18,62; 25,49</t>
+          <t>18,42; 25,52</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17,76; 25,26</t>
+          <t>18,14; 25,42</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>28,19; 34,85</t>
+          <t>28,37; 35,01</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>34,64%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,54; 18,35</t>
+          <t>12,41; 18,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,98; 20,38</t>
+          <t>14,41; 20,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,75; 19,79</t>
+          <t>13,84; 20,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27,66; 35,55</t>
+          <t>29,0; 36,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,5; 20,47</t>
+          <t>14,34; 20,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,26; 19,9</t>
+          <t>13,75; 19,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,4; 22,73</t>
+          <t>16,16; 22,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>35,03; 76,13</t>
+          <t>33,07; 39,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,2; 18,29</t>
+          <t>14,07; 18,21</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15,07; 19,37</t>
+          <t>15,03; 19,35</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15,95; 20,38</t>
+          <t>15,58; 19,92</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>32,86; 62,83</t>
+          <t>32,01; 37,15</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>39,49%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,69; 18,01</t>
+          <t>12,95; 17,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,36; 18,87</t>
+          <t>13,15; 18,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,89; 14,5</t>
+          <t>9,66; 14,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,92; 39,6</t>
+          <t>33,71; 40,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,34; 17,65</t>
+          <t>12,21; 17,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,59; 18,86</t>
+          <t>13,6; 18,68</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,54; 16,75</t>
+          <t>11,42; 16,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>39,03; 45,58</t>
+          <t>38,53; 44,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,36; 17,03</t>
+          <t>13,29; 16,98</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14,23; 18,13</t>
+          <t>14,36; 17,99</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11,37; 14,79</t>
+          <t>11,2; 14,62</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,35; 41,15</t>
+          <t>37,18; 41,74</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12,76; 14,97</t>
+          <t>12,72; 15,11</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,42; 19,03</t>
+          <t>16,35; 19,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14,64; 17,0</t>
+          <t>14,52; 16,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22,0; 31,62</t>
+          <t>29,39; 32,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,63; 17,03</t>
+          <t>14,51; 17,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,97; 19,6</t>
+          <t>16,91; 19,58</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,03; 18,73</t>
+          <t>15,94; 18,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>34,77; 49,92</t>
+          <t>34,72; 37,58</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14,03; 15,72</t>
+          <t>14,02; 15,75</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16,91; 18,89</t>
+          <t>17,03; 18,95</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15,65; 17,44</t>
+          <t>15,68; 17,44</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>31,01; 40,25</t>
+          <t>32,54; 34,59</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88939</t>
+          <t>90308</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>104967</t>
+          <t>105535</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>193905</t>
+          <t>195842</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>29205; 52450</t>
+          <t>29033; 51056</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>37373; 63472</t>
+          <t>36926; 64442</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31149; 56833</t>
+          <t>32233; 56170</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>71781; 106535</t>
+          <t>75672; 107809</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21253; 42686</t>
+          <t>21509; 43009</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35588; 62556</t>
+          <t>34927; 61522</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34976; 62467</t>
+          <t>34942; 61236</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>92515; 118940</t>
+          <t>92958; 118193</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>55801; 87018</t>
+          <t>56448; 88920</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>77853; 118129</t>
+          <t>77674; 116229</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>71444; 110423</t>
+          <t>73405; 109244</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>174264; 216546</t>
+          <t>176439; 217032</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>139642</t>
+          <t>145392</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>161149</t>
+          <t>167372</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>300791</t>
+          <t>312764</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>38743; 66347</t>
+          <t>38431; 67049</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>73517; 110594</t>
+          <t>73310; 109005</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64819; 97940</t>
+          <t>63511; 96100</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>116303; 163911</t>
+          <t>122729; 167862</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>48729; 76636</t>
+          <t>49566; 78226</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>74475; 109852</t>
+          <t>74265; 110203</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55402; 86550</t>
+          <t>54751; 87949</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>142478; 179434</t>
+          <t>147476; 187024</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>94227; 134998</t>
+          <t>94696; 134870</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>153784; 205315</t>
+          <t>153561; 207851</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>124574; 174424</t>
+          <t>129112; 175923</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>271377; 333163</t>
+          <t>285460; 345172</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86636</t>
+          <t>85263</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>108912</t>
+          <t>111383</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>195548</t>
+          <t>196645</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>36645; 62692</t>
+          <t>35890; 60582</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>53087; 82582</t>
+          <t>54245; 84166</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47485; 73869</t>
+          <t>47288; 74316</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>71874; 100563</t>
+          <t>73570; 99091</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>49544; 78366</t>
+          <t>48840; 77918</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>50458; 79161</t>
+          <t>48842; 79349</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57702; 89600</t>
+          <t>58740; 89729</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>94123; 122824</t>
+          <t>96684; 126023</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>93328; 130501</t>
+          <t>93116; 132509</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>111325; 152660</t>
+          <t>110195; 150561</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>114399; 155894</t>
+          <t>111075; 151880</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>175578; 217095</t>
+          <t>175150; 214776</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100909</t>
+          <t>109110</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>137284</t>
+          <t>147890</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>238193</t>
+          <t>257000</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33169; 56365</t>
+          <t>32275; 56791</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51488; 83142</t>
+          <t>51994; 83698</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>57422; 87550</t>
+          <t>57628; 87694</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>82835; 119202</t>
+          <t>88561; 129144</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>49224; 76025</t>
+          <t>48741; 76125</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>76627; 110358</t>
+          <t>78112; 109969</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>67365; 99910</t>
+          <t>67732; 102010</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>80836; 173707</t>
+          <t>131389; 166067</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>88571; 124267</t>
+          <t>87409; 123637</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>135796; 184772</t>
+          <t>136302; 181440</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>129577; 178476</t>
+          <t>131176; 175766</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>171174; 278664</t>
+          <t>231544; 280954</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55996</t>
+          <t>59740</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>81042</t>
+          <t>85664</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>137038</t>
+          <t>145404</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>21986; 42512</t>
+          <t>23055; 42825</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24800; 48457</t>
+          <t>25758; 48273</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19478; 38664</t>
+          <t>19092; 38383</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46315; 66591</t>
+          <t>49245; 71535</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>30826; 53814</t>
+          <t>30581; 53562</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30909; 55455</t>
+          <t>32353; 55685</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20914; 42598</t>
+          <t>21316; 42653</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>71444; 90516</t>
+          <t>75029; 95953</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>58114; 89512</t>
+          <t>59174; 89603</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>62895; 96150</t>
+          <t>63972; 95007</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43947; 73611</t>
+          <t>44775; 72569</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>124247; 150431</t>
+          <t>130505; 159515</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>71163</t>
+          <t>71241</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>95084</t>
+          <t>97781</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>166247</t>
+          <t>169022</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>25340; 47373</t>
+          <t>25709; 48171</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>45325; 73968</t>
+          <t>46488; 73493</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>38399; 63893</t>
+          <t>39702; 64828</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>59758; 83287</t>
+          <t>60222; 83819</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>36482; 62721</t>
+          <t>37810; 63956</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>51276; 78694</t>
+          <t>51258; 81220</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50435; 78469</t>
+          <t>51309; 79060</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>84117; 106333</t>
+          <t>84745; 108846</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>68994; 102727</t>
+          <t>68333; 103099</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>103148; 141204</t>
+          <t>102025; 141401</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>95226; 135454</t>
+          <t>97256; 136291</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>148471; 183570</t>
+          <t>151652; 187113</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>197308</t>
+          <t>235613</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>438752</t>
+          <t>281112</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>636060</t>
+          <t>516725</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>77020; 112725</t>
+          <t>76241; 112092</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>92674; 135088</t>
+          <t>95516; 136298</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>90298; 129954</t>
+          <t>90862; 131323</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>172680; 221961</t>
+          <t>208707; 265920</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>92520; 130636</t>
+          <t>91512; 130385</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>98909; 138082</t>
+          <t>95388; 138634</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>113346; 157134</t>
+          <t>111739; 154716</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>297467; 646574</t>
+          <t>255282; 306406</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>177884; 229114</t>
+          <t>176238; 228059</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>204398; 262817</t>
+          <t>203952; 262559</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>214920; 274718</t>
+          <t>210014; 268470</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>484226; 925864</t>
+          <t>477510; 554208</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>262849</t>
+          <t>295768</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>301387</t>
+          <t>347317</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>564236</t>
+          <t>643085</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>94366; 133940</t>
+          <t>96299; 133234</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>103779; 146643</t>
+          <t>102214; 144479</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>76996; 112884</t>
+          <t>75195; 111710</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>119976; 367764</t>
+          <t>269009; 323603</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>96679; 138294</t>
+          <t>95645; 138913</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>111937; 155344</t>
+          <t>112078; 153894</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>95324; 138346</t>
+          <t>94380; 139906</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>279244; 326040</t>
+          <t>320021; 372380</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>204039; 260040</t>
+          <t>202924; 259339</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>227879; 290242</t>
+          <t>229874; 288035</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>182422; 237269</t>
+          <t>179791; 234560</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>350951; 676617</t>
+          <t>605547; 679751</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1003443</t>
+          <t>1092435</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1428576</t>
+          <t>1344053</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2432019</t>
+          <t>2436488</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>417913; 490096</t>
+          <t>416507; 494851</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>561934; 651223</t>
+          <t>559303; 651651</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>496907; 576882</t>
+          <t>492829; 574832</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>761251; 1094074</t>
+          <t>1038257; 1148687</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>494083; 574991</t>
+          <t>490061; 578056</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>603682; 697331</t>
+          <t>601675; 696575</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>568059; 664023</t>
+          <t>564882; 667564</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1272239; 1826627</t>
+          <t>1296631; 1403302</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>933527; 1045896</t>
+          <t>932541; 1048028</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1180465; 1318056</t>
+          <t>1188590; 1322663</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1085633; 1210414</t>
+          <t>1088262; 1210238</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2207379; 2865676</t>
+          <t>2365011; 2513361</t>
         </is>
       </c>
     </row>
